--- a/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductPriceData.xlsx
+++ b/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductPriceData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>主料號</t>
   </si>
@@ -167,6 +167,15 @@
       <t>不可空白</t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品 ID</t>
+  </si>
+  <si>
+    <t>ProductId</t>
+  </si>
+  <si>
+    <t>{{Products.ProductId}}</t>
   </si>
 </sst>
 </file>
@@ -573,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.875" style="1" customWidth="1"/>
@@ -591,7 +600,7 @@
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="5" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -631,8 +640,11 @@
       <c r="M1" s="11" t="s">
         <v>10</v>
       </c>
+      <c r="N1" s="11" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -672,8 +684,11 @@
       <c r="M2" s="14" t="s">
         <v>23</v>
       </c>
+      <c r="N2" s="14" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -712,6 +727,9 @@
       </c>
       <c r="M3" s="14" t="s">
         <v>36</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductPriceData.xlsx
+++ b/src/EtheriT.Coker.Application/Resources/ProductExportTemplates/ProductPriceData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\易碩\專案\newCoker\EtheriT.Coker.WebApplication\src\EtheriT.Coker.Application\Resources\ProductExportTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A95582D-9FE3-49B4-AAA3-006C76C8C41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225C36EA-74AB-42A6-813E-B89EF09ECCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>主料號</t>
   </si>
@@ -176,6 +176,15 @@
   </si>
   <si>
     <t>{{Products.ProductId}}</t>
+  </si>
+  <si>
+    <t>建議售價</t>
+  </si>
+  <si>
+    <t>SuggestPrice</t>
+  </si>
+  <si>
+    <t>{{Products.SuggestPrice}}</t>
   </si>
 </sst>
 </file>
@@ -582,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.875" style="1" customWidth="1"/>
@@ -600,7 +609,7 @@
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="5" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -632,19 +641,22 @@
         <v>8</v>
       </c>
       <c r="K1" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="M1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="N1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -675,20 +687,23 @@
       <c r="J2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="M2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="O2" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -719,16 +734,19 @@
       <c r="J3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="M3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="N3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="O3" s="14" t="s">
         <v>41</v>
       </c>
     </row>
